--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -64,6 +64,24 @@
   </si>
   <si>
     <t>Признаки по видам экономической деятельности (приставка _s - sector)</t>
+  </si>
+  <si>
+    <t>Численность работников, выполнявших научные исследования и разработки</t>
+  </si>
+  <si>
+    <t>researchers_s</t>
+  </si>
+  <si>
+    <t>2017-2024</t>
+  </si>
+  <si>
+    <t>11_ОКВЭД2_публ.xlsx</t>
+  </si>
+  <si>
+    <t>1_2 ОКВЭД2_публ.xlsx</t>
+  </si>
+  <si>
+    <t>Исходник-форма (росстат)</t>
   </si>
 </sst>
 </file>
@@ -412,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -421,14 +439,15 @@
     <col min="4" max="4" width="19.140625" customWidth="1"/>
     <col min="5" max="5" width="21.5703125" customWidth="1"/>
     <col min="6" max="6" width="25.28515625" customWidth="1"/>
+    <col min="7" max="7" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,8 +466,11 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -467,8 +489,11 @@
       <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -486,6 +511,32 @@
       </c>
       <c r="F4" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1814</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -82,13 +82,28 @@
   </si>
   <si>
     <t>Исходник-форма (росстат)</t>
+  </si>
+  <si>
+    <t>AIcosts_s</t>
+  </si>
+  <si>
+    <t>Затраты на внедрение и использование искусственного интеллекта</t>
+  </si>
+  <si>
+    <t>млн. руб.</t>
+  </si>
+  <si>
+    <t>47_ОКВЭД.xlsx</t>
+  </si>
+  <si>
+    <t>Финансовые признаки</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,16 +129,30 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -131,11 +160,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -150,6 +194,16 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -430,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -443,7 +497,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -537,6 +591,40 @@
       </c>
       <c r="G5" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2024</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2102</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -97,6 +97,15 @@
   </si>
   <si>
     <t>Финансовые признаки</t>
+  </si>
+  <si>
+    <t>ITcosts_s</t>
+  </si>
+  <si>
+    <t>Затраты организации на внедрение и использование цифровых технологий, всего</t>
+  </si>
+  <si>
+    <t>2016-2024</t>
   </si>
 </sst>
 </file>
@@ -484,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -627,6 +636,29 @@
         <v>24</v>
       </c>
     </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="7">
+        <v>9426</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -106,6 +106,15 @@
   </si>
   <si>
     <t>2016-2024</t>
+  </si>
+  <si>
+    <t>Skvozcosts_s</t>
+  </si>
+  <si>
+    <t>Затраты на "сквозные" цифровые технологии</t>
+  </si>
+  <si>
+    <t>2020-2024</t>
   </si>
 </sst>
 </file>
@@ -188,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -212,6 +221,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -493,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -659,6 +671,29 @@
         <v>24</v>
       </c>
     </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1796</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -662,7 +662,7 @@
         <v>28</v>
       </c>
       <c r="E8" s="7">
-        <v>9426</v>
+        <v>8111</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -108,13 +108,19 @@
     <t>2016-2024</t>
   </si>
   <si>
-    <t>Skvozcosts_s</t>
-  </si>
-  <si>
     <t>Затраты на "сквозные" цифровые технологии</t>
   </si>
   <si>
     <t>2020-2024</t>
+  </si>
+  <si>
+    <t>trainingcosts_s</t>
+  </si>
+  <si>
+    <t>skvozcosts_s</t>
+  </si>
+  <si>
+    <t>Затраты на обучение сотрудников, связанное с внедрением и использованием цифровых технологий</t>
   </si>
 </sst>
 </file>
@@ -505,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -673,16 +679,16 @@
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>30</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" s="7">
         <v>1796</v>
@@ -691,6 +697,29 @@
         <v>10</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3996</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>24</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -565,7 +565,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="2">
-        <v>1672</v>
+        <v>1567</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -588,7 +588,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="2">
-        <v>1672</v>
+        <v>1567</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>10</v>
@@ -611,7 +611,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="2">
-        <v>1814</v>
+        <v>1707</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>10</v>
@@ -645,7 +645,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="7">
-        <v>2102</v>
+        <v>1965</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>10</v>
@@ -668,7 +668,7 @@
         <v>28</v>
       </c>
       <c r="E8" s="7">
-        <v>8111</v>
+        <v>7579</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>10</v>
@@ -691,7 +691,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="7">
-        <v>1796</v>
+        <v>1595</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>10</v>
@@ -714,7 +714,7 @@
         <v>28</v>
       </c>
       <c r="E10" s="7">
-        <v>3996</v>
+        <v>3641</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -121,6 +121,18 @@
   </si>
   <si>
     <t>Затраты на обучение сотрудников, связанное с внедрением и использованием цифровых технологий</t>
+  </si>
+  <si>
+    <t>4_ОКВЭД.xlsx</t>
+  </si>
+  <si>
+    <t>Затраты на научные исследования и разработки, всего</t>
+  </si>
+  <si>
+    <t>RDcosts_s</t>
+  </si>
+  <si>
+    <t>2017-2025</t>
   </si>
 </sst>
 </file>
@@ -511,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -631,44 +643,44 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="7">
-        <v>2024</v>
+      <c r="D7" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="E7" s="7">
-        <v>1965</v>
+        <v>1660</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>28</v>
+      <c r="D8" s="7">
+        <v>2024</v>
       </c>
       <c r="E8" s="7">
-        <v>7579</v>
+        <v>1965</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>10</v>
@@ -677,21 +689,21 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" s="7">
-        <v>1595</v>
+        <v>7579</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>10</v>
@@ -700,26 +712,49 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7">
-        <v>3641</v>
+        <v>1595</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="G10" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3641</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>24</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -132,7 +132,16 @@
     <t>RDcosts_s</t>
   </si>
   <si>
-    <t>2017-2025</t>
+    <t>RDsalary_s</t>
+  </si>
+  <si>
+    <t>RDequip_s</t>
+  </si>
+  <si>
+    <t>Затраты на оплату труда (научные разработки), всего</t>
+  </si>
+  <si>
+    <t>Затраты на оборудование (научные разработки), всего</t>
   </si>
 </sst>
 </file>
@@ -523,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -643,44 +652,44 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>37</v>
+      <c r="D7" s="7">
+        <v>2024</v>
       </c>
       <c r="E7" s="7">
-        <v>1660</v>
+        <v>1965</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7">
-        <v>2024</v>
+      <c r="D8" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="E8" s="7">
-        <v>1965</v>
+        <v>7579</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>10</v>
@@ -689,21 +698,21 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="7">
-        <v>7579</v>
+        <v>1595</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>10</v>
@@ -712,21 +721,21 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E10" s="7">
-        <v>1595</v>
+        <v>3641</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>10</v>
@@ -735,27 +744,73 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E11" s="7">
-        <v>3641</v>
+        <v>1660</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>24</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1658</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1656</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -96,9 +96,6 @@
     <t>47_ОКВЭД.xlsx</t>
   </si>
   <si>
-    <t>Финансовые признаки</t>
-  </si>
-  <si>
     <t>ITcosts_s</t>
   </si>
   <si>
@@ -142,6 +139,33 @@
   </si>
   <si>
     <t>Затраты на оборудование (научные разработки), всего</t>
+  </si>
+  <si>
+    <t>AIusage_s</t>
+  </si>
+  <si>
+    <t>Число организаций, использовавших ИИ</t>
+  </si>
+  <si>
+    <t>2021-2024</t>
+  </si>
+  <si>
+    <t>1_ОКВЭД.xlsx</t>
+  </si>
+  <si>
+    <t>BDusage_s</t>
+  </si>
+  <si>
+    <t>Число организаций, использовавших технологии сбора, обработки и анализа больших данных</t>
+  </si>
+  <si>
+    <t>Группа: Признаки внедрения и использования</t>
+  </si>
+  <si>
+    <t>Группа: Финансовые признаки</t>
+  </si>
+  <si>
+    <t>Группа: Человеческий капитал</t>
   </si>
 </sst>
 </file>
@@ -183,7 +207,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,6 +217,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -224,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -234,9 +270,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -246,11 +279,29 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -545,7 +596,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -572,245 +623,313 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="11">
+        <v>8605</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="11">
+        <v>6456</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E6" s="2">
         <v>1567</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E8" s="16">
         <v>1567</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F8" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E9" s="16">
         <v>1707</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1965</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1965</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="D12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="6">
+        <v>7579</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="8" t="s">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1595</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E14" s="6">
+        <v>3641</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="7">
-        <v>7579</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1660</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1595</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="D16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1658</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="7" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3641</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="7">
-        <v>1660</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1658</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="7">
+      <c r="E17" s="6">
         <v>1656</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>34</v>
+      <c r="F17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -166,6 +166,24 @@
   </si>
   <si>
     <t>Группа: Человеческий капитал</t>
+  </si>
+  <si>
+    <t>ITusage_s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Число организаций, использовавших цифровые технологии, всего </t>
+  </si>
+  <si>
+    <t>inetusage_s</t>
+  </si>
+  <si>
+    <t>Число организаций, использовавших интернет</t>
+  </si>
+  <si>
+    <t>PCusage_s</t>
+  </si>
+  <si>
+    <t>Число организаций, использовавших персональные компьютеры</t>
   </si>
 </sst>
 </file>
@@ -207,7 +225,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,6 +247,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,12 +289,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -302,6 +320,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -583,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -596,7 +620,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -624,311 +648,380 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="9">
+        <v>9397</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E5" s="9">
         <v>8605</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="F5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E6" s="9">
         <v>6456</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="11" t="s">
+      <c r="F6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1567</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-    </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="16">
-        <v>1567</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>19</v>
+      <c r="D7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="9">
+        <v>9397</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="9">
+        <v>9397</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="16">
+        <v>1567</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1567</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C12" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E12" s="14">
         <v>1707</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="16" t="s">
+      <c r="F12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D14" s="4">
         <v>2024</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E14" s="4">
         <v>1965</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E15" s="4">
         <v>7579</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E16" s="4">
         <v>1595</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="F16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E17" s="4">
         <v>3641</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="F17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E18" s="4">
         <v>1660</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="F18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E19" s="4">
         <v>1658</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="s">
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E20" s="4">
         <v>1656</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="F20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>33</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -184,6 +184,21 @@
   </si>
   <si>
     <t>Число организаций, использовавших персональные компьютеры</t>
+  </si>
+  <si>
+    <t>Группа: Производство</t>
+  </si>
+  <si>
+    <t>factoriescap_s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Объем отгруженных товаров собственного производства, выполненных работ и услуг собственными силами </t>
+  </si>
+  <si>
+    <t>2017-2025</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -225,7 +240,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,6 +268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -284,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -325,6 +346,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -1025,6 +1056,40 @@
         <v>33</v>
       </c>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="20">
+        <v>1179</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="63">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -198,7 +198,16 @@
     <t>2017-2025</t>
   </si>
   <si>
-    <t>-</t>
+    <t>VDS_s</t>
+  </si>
+  <si>
+    <t>Валовая добавленная стоимость по отраслям экономики</t>
+  </si>
+  <si>
+    <t>Национальные счета (Росстат)</t>
+  </si>
+  <si>
+    <t>Промышленное производство (Росстат)</t>
   </si>
 </sst>
 </file>
@@ -638,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -1086,8 +1095,31 @@
       <c r="F22" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
         <v>59</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="20">
+        <v>171</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
+    <sheet name="По регионам" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="68">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -208,6 +209,21 @@
   </si>
   <si>
     <t>Промышленное производство (Росстат)</t>
+  </si>
+  <si>
+    <t>region, okato, year, value</t>
+  </si>
+  <si>
+    <t>1_ОКАТО.xlsx</t>
+  </si>
+  <si>
+    <t>AIusage_r</t>
+  </si>
+  <si>
+    <t>BDusage_r</t>
+  </si>
+  <si>
+    <t>ITusage_r</t>
   </si>
 </sst>
 </file>
@@ -314,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -366,6 +382,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1126,4 +1145,127 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.140625" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="9">
+        <v>376</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="9">
+        <v>376</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -224,6 +224,15 @@
   </si>
   <si>
     <t>ITusage_r</t>
+  </si>
+  <si>
+    <t>Признаки по регионам РФ (приставка _r - region)</t>
+  </si>
+  <si>
+    <t>inetusage_r</t>
+  </si>
+  <si>
+    <t>PCusage_r</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -1163,7 +1172,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1213,8 +1222,12 @@
       <c r="D4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="E4" s="9">
+        <v>752</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>64</v>
       </c>
@@ -1262,6 +1275,52 @@
         <v>63</v>
       </c>
       <c r="G6" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="9">
+        <v>752</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="9">
+        <v>752</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>64</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="76">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -233,6 +233,21 @@
   </si>
   <si>
     <t>PCusage_r</t>
+  </si>
+  <si>
+    <t>AIcosts_r</t>
+  </si>
+  <si>
+    <t>ITcosts_r</t>
+  </si>
+  <si>
+    <t>skvozcosts_r</t>
+  </si>
+  <si>
+    <t>trainingcosts_r</t>
+  </si>
+  <si>
+    <t>47_ОКАТО.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -1324,6 +1339,105 @@
         <v>64</v>
       </c>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E13" s="4">
+        <v>94</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="4">
+        <v>470</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -1386,7 +1386,9 @@
       <c r="D14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4">
+        <v>846</v>
+      </c>
       <c r="F14" s="4" t="s">
         <v>63</v>
       </c>
@@ -1430,7 +1432,9 @@
       <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <v>846</v>
+      </c>
       <c r="F16" s="4" t="s">
         <v>63</v>
       </c>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="78">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -248,6 +248,12 @@
   </si>
   <si>
     <t>47_ОКАТО.xlsx</t>
+  </si>
+  <si>
+    <t>VDS_r</t>
+  </si>
+  <si>
+    <t>Валовая добавленная стоимость по регионам РФ</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -1442,6 +1448,59 @@
         <v>75</v>
       </c>
     </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="20">
+        <v>846</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -254,6 +254,36 @@
   </si>
   <si>
     <t>Валовая добавленная стоимость по регионам РФ</t>
+  </si>
+  <si>
+    <r>
+      <t>Объем отгруженных товаров собственного производства, выполненных работ и услуг собственными силами (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>СУММА</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>factoriescap_r</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -1448,60 +1478,65 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-    </row>
-    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="20">
+        <v>752</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
+      <c r="D19" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="20">
+        <v>846</v>
+      </c>
       <c r="F19" s="20" t="s">
         <v>63</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="20">
-        <v>846</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="21" t="s">
         <v>61</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="84">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -284,6 +284,18 @@
   </si>
   <si>
     <t>factoriescap_r</t>
+  </si>
+  <si>
+    <t>1_2 ОКАТО_публ.xlsx</t>
+  </si>
+  <si>
+    <t>researchorg_r</t>
+  </si>
+  <si>
+    <t>researchersavg_r</t>
+  </si>
+  <si>
+    <t>researchers_r</t>
   </si>
 </sst>
 </file>
@@ -390,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -444,6 +456,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1209,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -1375,55 +1393,110 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="16">
+        <v>658</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="14">
+        <v>658</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E13" s="4">
-        <v>94</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>75</v>
-      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>27</v>
+      <c r="D14" s="4">
+        <v>2024</v>
       </c>
       <c r="E14" s="4">
-        <v>846</v>
+        <v>94</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>63</v>
@@ -1432,21 +1505,21 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>28</v>
+        <v>72</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" s="4">
-        <v>470</v>
+        <v>846</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>63</v>
@@ -1455,21 +1528,21 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="4">
-        <v>846</v>
+        <v>470</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>63</v>
@@ -1478,60 +1551,83 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="4">
+        <v>846</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-    </row>
-    <row r="18" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B19" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="20">
-        <v>752</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>23</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E19" s="20">
-        <v>846</v>
+        <v>752</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>63</v>
       </c>
       <c r="G19" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="20">
+        <v>846</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="21" t="s">
         <v>61</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="85">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>researchers_r</t>
+  </si>
+  <si>
+    <t>11_ОКАТО_публ.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1461,14 +1464,16 @@
         <v>13</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="14"/>
+        <v>27</v>
+      </c>
+      <c r="E12" s="14">
+        <v>846</v>
+      </c>
       <c r="F12" s="14" t="s">
         <v>63</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="89">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -299,6 +299,18 @@
   </si>
   <si>
     <t>11_ОКАТО_публ.xlsx</t>
+  </si>
+  <si>
+    <t>RDcosts_r</t>
+  </si>
+  <si>
+    <t>RDsalary_r</t>
+  </si>
+  <si>
+    <t>RDequip_r</t>
+  </si>
+  <si>
+    <t>4_ОКАТО.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
@@ -1579,60 +1591,129 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="4">
+        <v>846</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="4">
+        <v>846</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="4">
+        <v>846</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-    </row>
-    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B22" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C22" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E22" s="20">
         <v>752</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F22" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="G22" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B23" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D23" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E23" s="20">
         <v>846</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F23" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G20" s="21" t="s">
+      <c r="G23" s="21" t="s">
         <v>61</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1225,7 +1225,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="20">
-        <v>171</v>
+        <v>513</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="90">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>4_ОКАТО.xlsx</t>
+  </si>
+  <si>
+    <t>Промышленное производство (Росстат), ЕМИСС</t>
   </si>
 </sst>
 </file>
@@ -1202,13 +1205,13 @@
         <v>58</v>
       </c>
       <c r="E22" s="20">
-        <v>1179</v>
+        <v>1207</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>Промышленное производство (Росстат), ЕМИСС</t>
+  </si>
+  <si>
+    <t>2024-2025</t>
   </si>
 </sst>
 </file>
@@ -1029,11 +1032,11 @@
       <c r="C14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4">
-        <v>2024</v>
+      <c r="D14" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="E14" s="4">
-        <v>1965</v>
+        <v>4084</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="91">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -1515,11 +1515,11 @@
       <c r="C14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4">
-        <v>2024</v>
+      <c r="D14" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="E14" s="4">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>63</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>2024-2025</t>
+  </si>
+  <si>
+    <t>2020-2025</t>
   </si>
 </sst>
 </file>
@@ -1079,10 +1082,10 @@
         <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="E16" s="4">
-        <v>1595</v>
+        <v>1915</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>2020-2025</t>
+  </si>
+  <si>
+    <t>2016-2025</t>
   </si>
 </sst>
 </file>
@@ -1059,10 +1062,10 @@
         <v>23</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="E15" s="4">
-        <v>7579</v>
+        <v>9211</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>10</v>
@@ -1105,10 +1108,10 @@
         <v>23</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="E17" s="4">
-        <v>3641</v>
+        <v>4260</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1591,10 +1591,10 @@
         <v>23</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="E17" s="4">
-        <v>846</v>
+        <v>939</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>63</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -1545,10 +1545,10 @@
         <v>23</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="E15" s="4">
-        <v>846</v>
+        <v>940</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>63</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>Затраты на "сквозные" цифровые технологии</t>
-  </si>
-  <si>
-    <t>2020-2024</t>
   </si>
   <si>
     <t>trainingcosts_s</t>
@@ -813,7 +810,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -824,10 +821,10 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
@@ -842,21 +839,21 @@
         <v>10</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>40</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>41</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="9">
         <v>8605</v>
@@ -865,21 +862,21 @@
         <v>10</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="9">
         <v>6456</v>
@@ -888,15 +885,15 @@
         <v>10</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
@@ -911,15 +908,15 @@
         <v>10</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>7</v>
@@ -934,7 +931,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -962,7 +959,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1019,7 +1016,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1039,7 +1036,7 @@
         <v>23</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="4">
         <v>4084</v>
@@ -1062,7 +1059,7 @@
         <v>23</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15" s="4">
         <v>9211</v>
@@ -1076,7 +1073,7 @@
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>28</v>
@@ -1085,7 +1082,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="4">
         <v>1915</v>
@@ -1099,16 +1096,16 @@
     </row>
     <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="4">
         <v>4260</v>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>23</v>
@@ -1140,15 +1137,15 @@
         <v>10</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>23</v>
@@ -1163,15 +1160,15 @@
         <v>10</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>23</v>
@@ -1186,12 +1183,12 @@
         <v>10</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1202,16 +1199,16 @@
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>56</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>57</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" s="20">
         <v>1207</v>
@@ -1220,15 +1217,15 @@
         <v>10</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>59</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>60</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>23</v>
@@ -1243,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1265,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1296,7 +1293,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1307,10 +1304,10 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
@@ -1322,64 +1319,64 @@
         <v>752</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="9">
         <v>376</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="9">
         <v>376</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
@@ -1391,18 +1388,18 @@
         <v>752</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>7</v>
@@ -1414,15 +1411,15 @@
         <v>752</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
@@ -1437,15 +1434,15 @@
         <v>658</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1456,7 +1453,7 @@
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>11</v>
@@ -1471,15 +1468,15 @@
         <v>658</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>15</v>
@@ -1494,15 +1491,15 @@
         <v>846</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1513,7 +1510,7 @@
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>22</v>
@@ -1522,21 +1519,21 @@
         <v>23</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="4">
         <v>188</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>26</v>
@@ -1545,21 +1542,21 @@
         <v>23</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15" s="4">
         <v>940</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>28</v>
@@ -1568,47 +1565,47 @@
         <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="E16" s="4">
-        <v>470</v>
+        <v>526</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="4">
         <v>939</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>23</v>
@@ -1620,18 +1617,18 @@
         <v>846</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>23</v>
@@ -1643,18 +1640,18 @@
         <v>846</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>23</v>
@@ -1666,15 +1663,15 @@
         <v>846</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1685,10 +1682,10 @@
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>23</v>
@@ -1700,18 +1697,18 @@
         <v>752</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>23</v>
@@ -1723,10 +1720,10 @@
         <v>846</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
